--- a/Commentaire.xlsx
+++ b/Commentaire.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6"/>
   <cols>
     <col width="18.19921875" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -1072,14 +1072,13 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>45818.97264768721</v>
+        <v>45818.97264768519</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Code fiche :</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>A</t>
@@ -1095,8 +1094,34 @@
           <t>A</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>45821.97687079617</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Code fiche :</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Commentaire.xlsx
+++ b/Commentaire.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6"/>
   <cols>
     <col width="18.19921875" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -1097,14 +1097,13 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>45821.97687079617</v>
+        <v>45821.97687079861</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Code fiche :</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>A</t>
@@ -1120,8 +1119,72 @@
           <t>A</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>45822.44465986111</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Code fiche :</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>comentario de ejemplo</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>45822.4449375858</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Code fiche :</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>comentario de ejemplo 2</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Commentaire.xlsx
+++ b/Commentaire.xlsx
@@ -2,42 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="84" yWindow="456" windowWidth="25440" windowHeight="14484" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Com" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="12"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <color rgb="FF262730"/>
-      <sz val="18"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="18"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -48,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -56,23 +48,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -145,7 +141,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -155,44 +151,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -219,32 +215,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -271,24 +249,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -300,142 +260,166 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -445,26 +429,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6"/>
-  <cols>
-    <col width="18.19921875" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
-    <col width="15.69921875" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
-    <col width="21.796875" bestFit="1" customWidth="1" style="3" min="3" max="4"/>
-    <col width="11.19921875" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
-    <col width="15.796875" bestFit="1" customWidth="1" style="3" min="6" max="6"/>
-    <col width="37" bestFit="1" customWidth="1" style="3" min="7" max="7"/>
-    <col width="106.19921875" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
-    <col width="17.5" bestFit="1" customWidth="1" style="3" min="9" max="9"/>
-  </cols>
+  <dimension ref="A1:M21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" ht="22.95" customHeight="1" s="3">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Code fiche :</t>
         </is>
@@ -479,29 +453,54 @@
           <t>Situation perso</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Famille</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Patrimoine</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Qualité relation/pb gestion</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Commentaire </t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Horodatage</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Utilisateur</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Commentaire</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Variables utilisées</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="2" t="n">
         <v>44539.54938969907</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -509,6 +508,7 @@
           <t>Code fiche :</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>A</t>
@@ -524,14 +524,20 @@
           <t>A</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">teste commentaire </t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="2" t="n">
         <v>44539.54948313657</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -569,9 +575,14 @@
           <t xml:space="preserve">teste commentaire </t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="2" t="n">
         <v>44539.54973596065</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -609,9 +620,14 @@
           <t xml:space="preserve">teste commentaire </t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="2" t="n">
         <v>44539.5500684838</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -649,9 +665,14 @@
           <t xml:space="preserve">teste commentaire </t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="2" t="n">
         <v>44539.62349224537</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -689,9 +710,14 @@
           <t>test commentaire</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="2" t="n">
         <v>44539.62561263889</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -729,9 +755,14 @@
           <t>teste com</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="2" t="n">
         <v>44572.667701875</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -769,9 +800,14 @@
           <t xml:space="preserve">tres bien </t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="2" t="n">
         <v>44572.68113134259</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -809,9 +845,14 @@
           <t>Revoir les règles dans ce cas, pour que les textes sur les formations internet et le mandat de protection future apparaissent</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="2" t="n">
         <v>44573.40961696759</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -849,9 +890,14 @@
           <t xml:space="preserve">ok </t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="2" t="n">
         <v>44602.62395417824</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -889,9 +935,14 @@
           <t xml:space="preserve">test </t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="n">
+      <c r="A12" s="2" t="n">
         <v>44623.4925544213</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -924,9 +975,15 @@
           <t>A</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="n">
+      <c r="A13" s="2" t="n">
         <v>45688.5228578125</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -964,9 +1021,14 @@
           <t>test 1</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="n">
+      <c r="A14" s="2" t="n">
         <v>45695.60427395834</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1004,9 +1066,14 @@
           <t>TEST Mélanie 7 février 2025</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="n">
+      <c r="A15" s="2" t="n">
         <v>45695.62405434027</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1044,9 +1111,14 @@
           <t>TEST 2 Mélanie 7 février 2025</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="n">
+      <c r="A16" s="2" t="n">
         <v>45763.48310722222</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1054,6 +1126,7 @@
           <t>Code fiche :</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>A</t>
@@ -1069,9 +1142,16 @@
           <t>A</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="n">
+      <c r="A17" s="2" t="n">
         <v>45818.97264768519</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1079,6 +1159,7 @@
           <t>Code fiche :</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>A</t>
@@ -1094,9 +1175,16 @@
           <t>A</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="n">
+      <c r="A18" s="2" t="n">
         <v>45821.97687079861</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1104,6 +1192,7 @@
           <t>Code fiche :</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>A</t>
@@ -1119,9 +1208,16 @@
           <t>A</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="n">
+      <c r="A19" s="2" t="n">
         <v>45822.44465986111</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1129,6 +1225,7 @@
           <t>Code fiche :</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>A</t>
@@ -1144,15 +1241,21 @@
           <t>A</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>comentario de ejemplo</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="n">
-        <v>45822.4449375858</v>
+      <c r="A20" s="2" t="n">
+        <v>45822.44493758102</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1185,8 +1288,48 @@
           <t>comentario de ejemplo 2</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2025-06-14 11:47:16</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>flo.oerlemans@epfedu.fr</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2025-06-14_114653_flooerlemans.pdf</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hola, esto es un ejemplo</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>['santé'], Seule, famille proche, Faible, []</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Commentaire.xlsx
+++ b/Commentaire.xlsx
@@ -1,37 +1,78 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\EPF\Hospt_alix\Hospitalix_Rep\HOSPITALIX\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3585D18A-DD52-4C69-A534-6FACBA5E759D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+  <si>
+    <t>Horodatage</t>
+  </si>
+  <si>
+    <t>Utilisateur</t>
+  </si>
+  <si>
+    <t>PDF</t>
+  </si>
+  <si>
+    <t>Commentaire</t>
+  </si>
+  <si>
+    <t>Variables utilisées</t>
+  </si>
+  <si>
+    <t>2025-06-14 11:49:41</t>
+  </si>
+  <si>
+    <t>flo.oerlemans@epfedu.fr</t>
+  </si>
+  <si>
+    <t>2025-06-14_114931_flooerlemans.pdf</t>
+  </si>
+  <si>
+    <t>comentario de ejemplo</t>
+  </si>
+  <si>
+    <t>['tuteur'], Seule, famille proche, Faible, []</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +87,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,66 +411,45 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="5" max="5" width="34.90625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Horodatage</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Utilisateur</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Commentaire</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Variables utilisées</t>
-        </is>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2025-06-14 11:49:41</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>flo.oerlemans@epfedu.fr</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2025-06-14_114931_flooerlemans.pdf</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>comentario de ejemplo</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>['tuteur'], Seule, famille proche, Faible, []</t>
-        </is>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Commentaire.xlsx
+++ b/Commentaire.xlsx
@@ -1,78 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\EPF\Hospt_alix\Hospitalix_Rep\HOSPITALIX\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3585D18A-DD52-4C69-A534-6FACBA5E759D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>Horodatage</t>
-  </si>
-  <si>
-    <t>Utilisateur</t>
-  </si>
-  <si>
-    <t>PDF</t>
-  </si>
-  <si>
-    <t>Commentaire</t>
-  </si>
-  <si>
-    <t>Variables utilisées</t>
-  </si>
-  <si>
-    <t>2025-06-14 11:49:41</t>
-  </si>
-  <si>
-    <t>flo.oerlemans@epfedu.fr</t>
-  </si>
-  <si>
-    <t>2025-06-14_114931_flooerlemans.pdf</t>
-  </si>
-  <si>
-    <t>comentario de ejemplo</t>
-  </si>
-  <si>
-    <t>['tuteur'], Seule, famille proche, Faible, []</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -87,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -411,46 +420,141 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="5" max="5" width="34.90625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Horodatage</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Utilisateur</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Commentaire</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Variables utilisées</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Santé/contexte</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Situation perso</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Famille</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Patrimoine</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Qualité relation/pb gestion</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025-06-14 11:49:41</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>flo.oerlemans@epfedu.fr</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2025-06-14_114931_flooerlemans.pdf</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>comentario de ejemplo</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>['tuteur'], Seule, famille proche, Faible, []</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2025-06-14 12:07:36</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>flo.oerlemans@epfedu.fr</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2025-06-14_120726_flooerlemans.pdf</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>comentario de ejemplo</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Commentaire.xlsx
+++ b/Commentaire.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,6 +556,50 @@
       </c>
       <c r="J3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025-06-14 12:09:47</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>flo.oerlemans@epfedu.fr</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2025-06-14_120931_flooerlemans.pdf</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>comentario de ejemplo</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Commentaire.xlsx
+++ b/Commentaire.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,6 +600,54 @@
       </c>
       <c r="J4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025-06-14 12:24:51</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>flo.oerlemans@epfedu.fr</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2025-06-14_122433_flooerlemans.pdf</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>otro ejemplo</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Commentaire.xlsx
+++ b/Commentaire.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -648,6 +648,563 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025-06-14 13:30:38</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>flo.oerlemans@epfedu.fr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2025-06-14_133009_flooerlemans.pdf</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>xdsaddasda;dkfs;dkfs;dkfs;dc,sd;csoifnscisoefm;esmdpoesfnevcms;csoenogiregerdpmdsf'sdflsfs';dl;sdclksmdlnvsudfsidljf;sfslfs'elfsefl
+sfes'efk;svcs;dc,s;djstjretiere;mlfdsmv;dfopjvd,v';r,d'rvd'rvd,mdo;kpg'gldr'gldr'lgd'plgd'rg</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025-06-14 13:56:11</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>flo.oerlemans@epfedu.fr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2025-06-14_135557_flooerlemans.pdf</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025-06-14 13:57:17</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>flo.oerlemans@epfedu.fr</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2025-06-14_135557_flooerlemans.pdf</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025-06-14 14:07:11</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>flo.oerlemans@epfedu.fr</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2025-06-14_140705_flooerlemans.pdf</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SDASDA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025-06-14 14:08:10</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>flo.oerlemans@epfedu.fr</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2025-06-14_140806_flooerlemans.pdf</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>dfsd</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-06-14 14:14:48</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>flo.oerlemans@epfedu.fr</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2025-06-14_141443_flooerlemans.pdf</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>dsfdsf</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-06-14 14:18:28</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>flo.oerlemans@epfedu.fr</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2025-06-14_141819_flooerlemans.pdf</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>hola comentario</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-06-14 14:21:21</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>flo.oerlemans@epfedu.fr</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2025-06-14_142113_flooerlemans.pdf</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>hola comentario</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-06-14 14:21:55</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>flo.oerlemans@epfedu.fr</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2025-06-14_142151_flooerlemans.pdf</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>hola comentario</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-06-14 14:25:45</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>flo.oerlemans@epfedu.fr</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2025-06-14_142539_flooerlemans.pdf</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>hola 2</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-06-14 14:40:11</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>erick_eapa@outlook.com</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2025-06-14_144001_erick_eapa.pdf</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>mi primer comentario</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-06-14 14:40:32</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>erick_eapa@outlook.com</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2025-06-14_144029_erick_eapa.pdf</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>mi primer comentario</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-06-14 14:40:38</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>erick_eapa@outlook.com</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2025-06-14_144035_erick_eapa.pdf</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>mi primer comentario</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Commentaire.xlsx
+++ b/Commentaire.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1205,6 +1205,54 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025-06-14 19:05:05</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>erick_eapa@outlook.com</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2025-06-14_190456_erick_eapa.pdf</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ejemplo ahora</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Commentaire.xlsx
+++ b/Commentaire.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1253,6 +1253,233 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2025-06-15 15:13:01</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>erick_eapa@outlook.com</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2025-06-15_151248_erick_eapa.pdf</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>This pdf was amazing :)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2025-06-16 13:51:36</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>flooerlemans16@gmail.com</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2025-06-16_135119_flooerlemans16.pdf</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>COUCOU</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025-06-16 20:23:22</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>erick_eapa@outlook.com</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2025-06-16_202156_erick_eapa.pdf</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>def top_n(client_id, model, df, n=5):
+    # Productos ya calificados por el cliente
+    rated_items = df[df['customer'] == client_id]['product'].tolist()
+    # Todos los productos
+    all_items = df['product'].unique()
+    # Filtrar productos que el cliente NO ha calificado
+    items_to_predict = [item for item in all_items if item not in rated_items]
+    # Predecir puntuación para cada uno de ellos
+    predictions = []
+    for item in items_to_predict:
+        pred = model.predict(uid=client_id, iid=item)
+        predictions.append((item, pred.est))  # (producto, puntuación estimada)
+    # Ordenar por puntuación descendente
+    predictions.sort(key=lambda x: x[1], reverse=True)
+    # Retornar los top n
+    return predictions[:n]</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2025-06-16 20:24:47</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>erick_eapa@outlook.com</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2025-06-16_202441_erick_eapa.pdf</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>dsfsdfs</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2025-06-16 21:06:16</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>erick_eapa@outlook.com</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2025-06-16_210607_erick_eapa.pdf</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>This is my comment</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Commentaire.xlsx
+++ b/Commentaire.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1480,6 +1480,130 @@
       </c>
       <c r="J24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025-06-17 02:02:17</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>flooerlemans16@gmail.com</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2025-06-17_020206_flooerlemans16.pdf</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>&amp;&amp;</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2025-06-17 02:05:58</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>flooerlemans16@gmail.com</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2025-06-17_020555_flooerlemans16.pdf</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2025-06-17 11:55:04</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>flooerlemans16@gmail.com</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2025-06-17_115443_flooerlemans16.pdf</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Commentaire.xlsx
+++ b/Commentaire.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1604,6 +1604,50 @@
       </c>
       <c r="J27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2025-06-19 15:52:01</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>flo.oerlemans@epfedu.fr</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2025-06-19_155155_flooerlemans.pdf</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LA la</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Commentaire.xlsx
+++ b/Commentaire.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1648,6 +1648,138 @@
       </c>
       <c r="J28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2025-06-19 18:09:52</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>erick_eapa@outlook.com</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2025-06-19_180944_erick_eapa.pdf</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>this is a sample comment</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2025-06-19 18:11:18</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>erick_eapa@outlook.com</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2025-06-19_181110_erick_eapa.pdf</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>this is a comment again</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2025-06-19 18:12:06</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>flo.oerlemans@epfedu.fr</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2025-06-19_181146_flooerlemans.pdf</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>What a report. thanks.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
